--- a/Excel/Project.xlsx
+++ b/Excel/Project.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Python\ExcelToJson\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\MineGlobe\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822389DE-F2F4-430E-B43D-2BD1FBBAFD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747A8693-8328-4FF0-9660-1618EECC3EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3849" yWindow="1843" windowWidth="16457" windowHeight="8426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -64,12 +64,6 @@
     <t>Turn-based combat framework with modular deck architecture and scalable gameplay systems.</t>
   </si>
   <si>
-    <t>Project_CardGame.html</t>
-  </si>
-  <si>
-    <t>../Raw/Img/project-cardgame.jpg</t>
-  </si>
-  <si>
     <t>Cooking Simulator</t>
   </si>
   <si>
@@ -82,19 +76,27 @@
     <t>Cooking Prototype</t>
   </si>
   <si>
-    <t>../cook/index.html</t>
-  </si>
-  <si>
-    <t>../spa.html</t>
-  </si>
-  <si>
-    <t>../touzi.html</t>
-  </si>
-  <si>
-    <t>Project_CookGame.html</t>
-  </si>
-  <si>
     <t>Restaurant simulation focused on AI customer behavior, cooking workflow and management mechanics.</t>
+  </si>
+  <si>
+    <t>Project/Project_CardGame.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Project/Project_CookGame.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Project/index.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Project/spa.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Project/touzi.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -464,10 +466,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -475,13 +474,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -489,10 +488,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -500,10 +499,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -511,10 +510,10 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Project.xlsx
+++ b/Excel/Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\MineGlobe\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747A8693-8328-4FF0-9660-1618EECC3EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DB2C22-16E1-493D-AD42-117FA57AA918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3849" yWindow="1843" windowWidth="16457" windowHeight="8426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Id</t>
   </si>
@@ -96,6 +96,13 @@
   </si>
   <si>
     <t>Project/touzi.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Survival Choice Game</t>
+  </si>
+  <si>
+    <t>Project/game.html</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -103,7 +110,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +124,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -139,8 +152,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -421,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -516,6 +530,20 @@
         <v>18</v>
       </c>
     </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/Project.xlsx
+++ b/Excel/Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\MineGlobe\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DB2C22-16E1-493D-AD42-117FA57AA918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3889C95C-A4EC-4392-A0F4-AEB8AB222EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3849" yWindow="1843" windowWidth="16457" windowHeight="8426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,14 +79,6 @@
     <t>Restaurant simulation focused on AI customer behavior, cooking workflow and management mechanics.</t>
   </si>
   <si>
-    <t>Project/Project_CardGame.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Project/Project_CookGame.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Project/index.html</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -103,6 +95,14 @@
   </si>
   <si>
     <t>Project/game.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Project/Project_CardGame.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Project/Project_CookGame.html</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -480,7 +480,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -494,7 +494,7 @@
         <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -505,7 +505,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -516,7 +516,7 @@
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.45">
@@ -535,13 +535,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
